--- a/推理框架/cards/vllm-full-session-review-technical-qa.xlsx
+++ b/推理框架/cards/vllm-full-session-review-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,13 +36,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">两卡各64 GB、预算比例0.9，可按128 GB作预算吗？</t>
+          <t xml:space="preserve">两卡各 64 GB、预算比例 0.9，可用总预算是多少？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；本题预算是115.2 GB，不能直接用设备总容量代替。
-[T#B,!c47f17#边界]：仅为给定比例的算术示例，实际账本还要区分单卡/总量与GB/GiB。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：给定两卡预算合计为 115.2 GB，不能用 128 GB 总容量代替。
+[E##2\times64\times0.9=115.2\ \mathrm{GB}]
+[T#B,!c47f17#边界]：这是给定比例下的总显存预算，不是扣除权重等占用后的 KV 专用预算；仍需统一单卡/总量与 GB/GiB 口径。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -59,13 +60,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">某个输入被padding放大85倍，整个模型显存也放大85倍吗？</t>
+          <t xml:space="preserve">局部 padding 倍率为何不能代表整体显存倍率？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能据此推断；倍率只对应发生该物化布局的局部数据。
-[T#B,!c47f17#边界]：模型总占用还包含权重、KV、其他激活及临时空间。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：局部倍率只描述特定物化布局的数据，不代表模型的总占用。
+• [T#B#整体账本]：还需分别计算权重、KV、其他激活与临时空间。
+[T#B,!c47f17#边界]：局部 padding 后的存储放大，也不能单独证明布局变换的数学等价。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -82,19 +84,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">b×K乘K×N的MatMul，常用FLOPs怎样计算？</t>
+          <t xml:space="preserve">(b×K) 乘 (K×N) 的 MatMul，常用 FLOPs 怎么算？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：按一次乘法加一次加法计2次浮点运算。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：按一次乘法加一次加法计 2 次浮点运算。
 [E##\mathrm{FLOPs}=2bKN]
 [T#B,!c47f17#边界]：使用常见乘加计数口径。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">乘加计作2次</t>
+          <t xml:space="preserve">乘加计作 2 次</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -106,19 +108,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BF16的(b×K)乘(K×N)，各输入读一次、输出写一次，理想流量怎么算？</t>
+          <t xml:space="preserve">BF16 的 A\[b,K\]×B\[K,N\]：各读一次、结果写一次，流量多少？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：把A、B的读取与C的写入都计入，每元素2字节。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：把 A、B 的读取与 C 的写入都计入，每元素 2 字节。
 [E##\mathrm{Bytes}=2(bK+KN+bN)]
-[T#B,!c47f17#边界]：A/B各读一次、C写一次，无额外读写；这不是实测流量。</t>
+[T#B,!c47f17#边界]：A/B 各读一次、C 写一次，无额外读写；这不是实测流量。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">输出仍是b×N</t>
+          <t xml:space="preserve">输出仍是 b×N</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -130,13 +132,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">访存变慢就足以判定bank conflict吗？</t>
+          <t xml:space="preserve">判定 bank conflict 还需要哪些证据？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不够；需确认存储层级、地址映射和相应观测证据。
-[T#B,!c47f17#边界]：不否定该项目可能存在冲突，只是不把类比和现象当作充分证据。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：需先确认存储层级、地址映射和相应观测证据。
+[T#B,!c47f17#边界]：访存变慢或布局相似只是线索，不能直接确定为 bank conflict。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -153,13 +155,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">temperature=0能保证整个推理过程完全确定吗？</t>
+          <t xml:space="preserve">temperature=0 排除了哪类随机性？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；它去掉采样选择中的随机性，不消除所有并发或Kernel不确定性。
-[T#B,!c47f17#边界]：相同采样策略不等于相同设备执行时序。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它去掉采样选择中的随机性。
+[T#B,!c47f17#边界]：并发、Kernel 或 Runtime 仍可能产生不确定性，不能据此保证整段推理完全确定。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -176,13 +178,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">加了tensor dump后异常消失，能证明数值计算原本正确吗？</t>
+          <t xml:space="preserve">加入 tensor dump 后异常消失，应怎样解读？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；dump可能改变时序或引入同步，使竞态不再复现。
-[T#B,!c47f17#边界]：这是排查同步问题的线索，不是具体根因的独立证明。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：dump 可能改变时序或引入同步，使异常暂时不再复现。
+[T#B,!c47f17#边界]：这是定位异步或竞态问题的线索，不是数值正确或具体根因的独立证明。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -199,12 +201,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么先找第一个分叉token，而不只比较最终输出？</t>
+          <t xml:space="preserve">排查生成差异，为何先找首个分叉 token？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：后续轨迹依赖前面的token和KV历史，后面的差异可能只是传播结果。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：后续轨迹依赖前面的 token 和 KV 历史，后面的差异可能只是传播结果。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -221,13 +223,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CPU padding尚未完成时，等待设备流能保证整次H2D完成吗？</t>
+          <t xml:space="preserve">Host padding 未完成时，流等待为何不能保证 H2D 完成？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；copy可能尚未提交到设备流，流等待未覆盖前置Host准备。
-[T#B,!c47f17#边界]：必须建立Host数据就绪、copy提交/完成与消费之间的依赖。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：等待设备流时，前置 CPU 准备或 H2D 提交可能尚未完成。
+• [T#B#依赖链]：Host 数据就绪 → copy 提交 → copy 完成 → 消费数据。
+[T#B,!c47f17#边界]：只等待流中已有任务，不能覆盖尚未完成的 Host 准备和未来提交。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -244,18 +247,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">多个设备stream就意味着CPU线程频繁切换吗？</t>
+          <t xml:space="preserve">设备 stream 数为何不能代表 CPU 线程切换次数？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能这样推断；stream与CPU线程不是一一对应关系。
-[T#B,!c47f17#边界]：跨流依赖、提交开销与线程切换需要分别核验。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：设备 stream 与 CPU 线程不是一一对应关系。
+[T#B,!c47f17#边界]：跨流 Event/Wait、提交开销与 CPU 线程切换应分别取证。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stream与线程分层</t>
+          <t xml:space="preserve">stream 与线程分层</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -267,13 +270,13 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个平台改单流更快，能推广为所有平台单流都更快吗？</t>
+          <t xml:space="preserve">单流优化的收益为何不能跨平台直接推广？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；减少依赖和提交开销的收益，要与放弃潜在overlap的代价比较。
-[T#B,!c47f17#边界]：依赖具体硬件能力、Runtime及workload。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；减少依赖和提交开销的收益，要与放弃潜在 overlap 的代价比较。
+[T#B,!c47f17#边界]：依赖具体硬件能力、Runtime 及 workload。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -297,7 +300,7 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：倍数是旧耗时除以新耗时；降幅是耗时减少量除以旧耗时。
 [E##\mathrm{speedup}=\frac{T_0}{T_1},\quad \mathrm{reduction}=1-\frac{T_1}{T_0}]
-[T#B,!c47f17#边界]：前后workload和计时边界必须可比。</t>
+[T#B,!c47f17#边界]：前后 workload 和计时边界必须可比。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -314,7 +317,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TP=2是否保证所有模型存储恰好各占一半？</t>
+          <t xml:space="preserve">TP=2 为何不保证模型存储恰好均分？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -336,12 +339,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么要先注册输出状态，再提交EngineCoreRequest？</t>
+          <t xml:space="preserve">提交 Core 请求前，为何先注册前端输出状态？</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：避免Core快速返回时，前端还没有该请求的输出处理状态和Collector关联。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：避免 Core 快速返回时，前端还没有该请求的输出处理状态和 Collector 关联。</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -351,20 +354,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C02；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C02；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">还没有模型输出时，Collector根据什么创建？</t>
+          <t xml:space="preserve">模型尚未返回时，Collector 用什么信息创建？</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：AsyncLLM可以用请求ID和output_kind创建空Collector。
-[T#B,!c47f17#边界]：创建接收器不依赖已经产生模型结果。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：AsyncLLM 可用请求 ID 和 output_kind 创建空 Collector。
+[T#B,!c47f17#边界]：先建立结果接收位置，不依赖模型已经产生输出。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -374,19 +377,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C02；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C02；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">新增请求跨IPC时，是EngineInput还是EngineCoreRequest？</t>
+          <t xml:space="preserve">新增请求跨 IPC 时使用哪种请求表示？</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：是EngineCoreRequest；Core再将它构造为内部可变Request。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：是 EngineCoreRequest；Core 再将它构造为内部可变 Request。</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -396,19 +399,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C01；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C01；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">grammar准备好后，请求就能直接RUNNING吗？</t>
+          <t xml:space="preserve">grammar 就绪后，还需通过哪些调度检查？</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；它只解除一个等待条件，仍要通过token budget和KV资源检查。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：仍需通过 token budget 和 KV 资源检查。
+[T#B,!c47f17#边界]：grammar 就绪只解除一个等待条件，不等于请求已取得全部执行资源。</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -418,20 +422,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C03；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C03；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">structured output每生成一个token都重新编译schema吗？</t>
+          <t xml:space="preserve">schema 编译与逐步准备 grammar mask 有何区别？</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；初始化或取得编译产物后，按请求推进匹配状态并准备本步mask。
-[T#B,!c47f17#边界]：缓存/初始化与每步约束准备是不同动作。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：编译产物可以初始化或复用；请求的匹配状态与本步 mask 则随生成推进。
+• [T#B#请求开始]：初始化/编译 schema，或取得可缓存的编译产物。
+• [T#B#逐步生成]：推进该请求的匹配状态，并准备本步合法 token mask。</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -441,14 +446,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C04；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C04；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON符合schema，就能保证填入的事实正确吗？</t>
+          <t xml:space="preserve">schema 合法为何不等于事实内容正确？</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -470,7 +475,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">调度后num_computed_tokens增加，能证明KV已算完吗？</t>
+          <t xml:space="preserve">num_computed_tokens 增加为何不代表 KV 已算完？</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -486,25 +491,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C06；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C06；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一个有效输出token来自最后一次prefill还是额外decode？</t>
+          <t xml:space="preserve">首个有效输出 token 在哪个计算阶段产生？</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：完成prompt的最后一次prefill即可产生首个有效输出token。
-[T#B,!c47f17#边界]：普通无投机生成；下一轮decode输入这个已采样token。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：完成 prompt 的最后一次 prefill 即可产生首个有效输出 token。
+[T#B,!c47f17#边界]：普通无投机生成；下一轮 decode 输入这个已采样 token。</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">最后prefill预测首token</t>
+          <t xml:space="preserve">最后 prefill 预测首 token</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -516,12 +521,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">开启chunked prefill后，每个prompt都必须拆成多块吗？</t>
+          <t xml:space="preserve">chunked prefill 是否要求每个 prompt 都分块？</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；它允许按预算拆分，短prompt也可能一次完成。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；它允许按预算拆分，短 prompt 也可能一次完成。</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -531,20 +536,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 R04；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 R04；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">preemption会产生用户可见的终止输出吗？</t>
+          <t xml:space="preserve">抢占与请求结束有什么区别？</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会仅因抢占而终止；请求及生成历史保留，等待资源恢复。
-[T#B,!c47f17#边界]：重算型抢占会重置相应计算进度。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：抢占保留请求和生成历史，等待恢复；不会仅因抢占就交付终止输出。
+[T#B,!c47f17#边界]：重算型抢占会重置相应计算进度；状态枚举与所在队列需分别观察。</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -554,19 +559,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C07；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C07；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">请求在waiting队列里，status就一定是WAITING吗？</t>
+          <t xml:space="preserve">waiting 队列与 WAITING 状态为何不能混同？</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不一定；被抢占的请求可以位于waiting队列，status仍为PREEMPTED。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不一定；被抢占的请求可以位于 waiting 队列，status 仍为 PREEMPTED。</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -576,43 +581,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 C07；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 C07；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">请求没进入本步InputBatch，是否必须删除CachedRequestState？</t>
+          <t xml:space="preserve">MRV1：退出本步 InputBatch 后还可保留什么状态？</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；未结束的请求可以退出本步batch，同时保留本地缓存供后续恢复。
-[T#B,!c47f17#边界]：保留旧块ID不代表仍拥有被抢占前的KV块。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：未结束请求可退出本步 batch，同时保留 CachedRequestState。
+[T#B,!c47f17#边界]：这是 MRV1 的状态分层；缓存中的旧 block ID 不代表仍拥有抢占前的 KV 块。</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">缓存集合大于本步batch</t>
+          <t xml:space="preserve">缓存集合大于本步 batch</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D01；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D01；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">resumed_req_ids中的请求，新block列表追加还是替换？</t>
+          <t xml:space="preserve">恢复请求时，新 block 列表为何替换旧列表？</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：替换旧列表；恢复载荷表达恢复后的完整映射。
-[T#B,!c47f17#边界]：普通继续执行时，新分配块通常按增量追加。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：恢复载荷给出恢复后的完整映射，所以应替换旧列表。
+[T#B,!c47f17#边界]：普通继续执行的载荷通常只包含新分配的增量块，采用追加语义。</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -622,26 +627,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D02；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D02；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">给定位置p、块大小B和块表T，KV槽位索引怎么算？</t>
+          <t xml:space="preserve">已知块表 T 和块大小 B，位置 p 的 KV 槽位怎么算？</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：先定位逻辑块，再叠加块内偏移。
 [E##\mathrm{slot}=T_{\lfloor p/B\rfloor}\,B+(p\bmod B)]
-[T#B,!c47f17#边界]：普通单组、分配块与kernel块大小相同；结果是token槽位，不是字节地址。</t>
+[T#B,!c47f17#边界]：普通单组、分配块与 kernel 块大小相同；结果是 token 槽位，不是字节地址。</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">块号乘B加偏移</t>
+          <t xml:space="preserve">块号乘 B 加偏移</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -653,7 +658,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">batch请求顺序改变，block table哪一维要同步重排？</t>
+          <t xml:space="preserve">batch 重排时，block table 的哪一维随之重排？</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -668,20 +673,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D05；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D05；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">query_start_loc与seq_lens分别表达什么？</t>
+          <t xml:space="preserve">query_start_loc 与 seq_lens 各表示什么？</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前者是本步展平query的请求片段边界，后者是对应请求的序列长度。
-[T#B,!c47f17#边界]：历史KV不应直接加进本步query片段长度。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：一个描述本步 Query 片段，另一个描述序列总长度。
+• [T#B#query_start_loc]：本步展平 Query 中，各请求片段的起止边界。
+• [T#B#seq_lens]：对应请求的序列长度；不要把历史 KV 长度加进本步 Query 片段。
+• [T#B#例子]：历史长度为 2、6，本步处理 3、1：Query 边界是 \[0,3,4\]，序列长度是 \[5,7\]。</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -691,20 +698,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D06；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D06；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">本步计算位置2到4，位置2的Query能读位置4的KV吗？</t>
+          <t xml:space="preserve">因果 Attention：同轮计算位置 2～4，位置 2 能读位置 4 的 KV 吗？</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：不能；同一批次计算不取消因果约束。
-[T#B,!c47f17#边界]：这里是普通因果Attention；也不能跨请求读取上下文。</t>
+[T#B,!c47f17#边界]：这里是普通因果 Attention；也不能跨请求读取上下文。</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -721,12 +728,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">两个step的shape相同，能沿用旧Attention metadata内容吗？</t>
+          <t xml:space="preserve">shape 相同，为何不能直接沿用旧 Attention metadata？</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能仅凭shape判断；内容必须对应本步请求、长度和KV映射。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能仅凭 shape 判断；内容必须对应本步请求、长度和 KV 映射。
 [T#B,!c47f17#边界]：缓冲可复用，不等于旧内容可直接复用。</t>
         </is>
       </c>
@@ -737,43 +744,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D07；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D07；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">找到统一Attention custom op，就确定实际kernel了吗？</t>
+          <t xml:space="preserve">从统一 Attention 入口如何追到实际 kernel？</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：没有；还要追选定backend、运行条件、布局和底层绑定。
-[T#B,!c47f17#边界]：选定实现不自动等于已证明性能最优。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：从统一入口继续核对所选 backend、运行条件、布局和底层绑定。
+[T#B,!c47f17#边界]：选中某个实现不代表已证明它在该 workload 上性能最优。</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">入口、backend、kernel分层</t>
+          <t xml:space="preserve">入口、backend、kernel 分层</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D08；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D08；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv_cache_dummy_dep不参与数值计算，能直接删除吗？</t>
+          <t xml:space="preserve">kv_cache_dummy_dep 不做数值计算，为何仍需保留？</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能仅据此删除；它可表达KV更新先于Attention读取的编译依赖。
-[T#B,!c47f17#边界]：所学具体路径；不是通用设备event或stream同步接口。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能仅据此删除；它可表达 KV 更新先于 Attention 读取的编译依赖。
+[T#B,!c47f17#边界]：所学具体路径；不是通用设备 event 或 stream 同步接口。</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -783,20 +790,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D09；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D09；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MRV1 execute_model返回None，是否表示模型执行失败？</t>
+          <t xml:space="preserve">MRV1 分离路径中，execute_model 返回 None 表示什么？</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是；在所学分离路径中，后续调用sample_tokens取得完整执行输出。
-[T#B,!c47f17#边界]：只针对该阶段协议，不推广到所有None返回。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：该阶段已计算并暂存 logits，尚未产生完整执行输出。
+• [T#B#后续阶段]：随后由 sample_tokens 应用采样约束并真正采样。
+[T#B,!c47f17#边界]：限定 MRV1 的所学分离路径；None 在此不是失败或轮询信号。</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -806,43 +814,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D10；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D10；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">sample_tokens只是取走已经采好的token吗？</t>
+          <t xml:space="preserve">sample_tokens 在 MRV1 分离路径中实际做什么？</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：不是；所学分离路径中，它应用采样约束并真正进行采样。
-[T#B,!c47f17#边界]：execute_model此前计算并暂存logits。</t>
+[T#B,!c47f17#边界]：execute_model 此前计算并暂存 logits。</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">logits与采样分开安排</t>
+          <t xml:space="preserve">logits 与采样分开安排</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D10；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D10；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通无投机生成，为什么不对每个输入位置都生成一个新token？</t>
+          <t xml:space="preserve">无投机生成时，哪些 hidden state 行用于生成 logits？</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个请求通常选本步片段末行的hidden state计算生成logits。
-[T#B,!c47f17#边界]：未完成prefill的候选不计作有效生成输出。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个请求通常选本步片段末行的 hidden state 计算生成 logits。
+[T#B,!c47f17#边界]：未完成 prefill 的候选不计作有效生成输出。</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -852,20 +860,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 D11；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 D11；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ModelRunner结果返回后，谁回写Core的token历史和结束状态？</t>
+          <t xml:space="preserve">执行结果由谁写回 Core 的请求账本？</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：EngineCore将执行结果交给Scheduler的结果更新逻辑回写和判停。
-[T#B,!c47f17#边界]：Runner本地状态不替代Scheduler的请求账本。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：EngineCore 将执行结果交给 Scheduler 的结果更新逻辑回写和判停。
+[T#B,!c47f17#边界]：Runner 本地状态不替代 Scheduler 的请求账本。</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -875,42 +883,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 R01、C01；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 R01、C01；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platform怎样指定自定义Worker？</t>
+          <t xml:space="preserve">Platform 通过哪个字段选择 Worker？</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：在check_and_update_config中设置parallel_config.worker_cls。
-[T#B,!c47f17#边界]：具体Runner再由Worker构造；限定所学版本的接入方式。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：在 check_and_update_config 中设置 parallel_config.worker_cls。
+[T#B,!c47f17#边界]：Runner 再由 Worker 构造；这是 v0.26.0 的接入方式。</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">平台配置Worker</t>
+          <t xml:space="preserve">平台配置 Worker</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 P01；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 P01；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platform返回自研Attention backend，会自动替换Worker吗？</t>
+          <t xml:space="preserve">Attention backend 与 Worker 是否由同一入口替换？</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；Attention backend选择与Worker类配置是不同入口。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不是：Attention backend 选择与 Worker 类配置是两个入口。</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -920,20 +928,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 P01；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 P01；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">注册torch.ops算子后，vLLM就会自动采用它吗？</t>
+          <t xml:space="preserve">torch.ops 注册后，还需什么才能被 vLLM 调用？</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；还要将对应vLLM模型算子调用路径接入该实现。
-[T#B,!c47f17#边界]：例如所学CustomOp的register_oot与forward_oot路径。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；还要将对应 vLLM 模型算子调用路径接入该实现。
+[T#B,!c47f17#边界]：例如所学 CustomOp 的 register_oot 与 forward_oot 路径。</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -943,42 +951,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 P03；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 P03；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">forward_native意味着在CPU执行吗？</t>
+          <t xml:space="preserve">forward_native 的 native 指什么？</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是；它表示原生PyTorch组合，执行设备取决于tensor与具体实现。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它表示原生 PyTorch 算子组合。
+[T#B,!c47f17#边界]：计算设备取决于 Tensor 与实际实现，不能把 native 理解成一定在 CPU 执行。</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">原生组合不等于CPU</t>
+          <t xml:space="preserve">原生组合不等于 CPU</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 P03；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 P03；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么collective不能只测试一个等于world的组？</t>
+          <t xml:space="preserve">collective 为何需要多个独立子组测试？</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：错误地忽略子组的实现也可能通过；需要多个独立子组暴露跨组归约。
-[T#B,!c47f17#边界]：TP=1还可能直接绕过通信。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：多个独立子组能暴露错误地跨组归约的实现。
+• [T#B#反例]：两组输入分别为 1、2 与 10、20；正确组内和应为 3、3、30、30。
+[T#B,!c47f17#边界]：只测试一个等于 world 的组可能漏错；TP=1 还可能绕过通信。</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -995,13 +1005,13 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">KV页因padding变大，就必须修改Scheduler吗？</t>
+          <t xml:space="preserve">KV 页 padding 增大时，应先检查哪层接口？</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；已有规格与页字节接口能准确表达时，应先在对应实现中兑现契约。
-[T#B,!c47f17#边界]：预算、实际布局和访问必须一致。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先检查已有 KV 规格与页字节接口能否准确表达物理占用。
+[T#B,!c47f17#边界]：能够表达时先修对应实现，使预算、布局和访问保持一致；padding 增大本身不足以要求修改 Scheduler。</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1011,20 +1021,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 P05；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 P05；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">主张core patch前，还要证明什么？</t>
+          <t xml:space="preserve">提出 Core 补丁前，要证明什么接口缺口？</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：证明需要的语义或保证无法通过现有字段、hook和机制表达。
-[T#B,!c47f17#边界]：换芯片、出现OOM或自定义Runner本身都不是充分证据。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：证明需要的语义或保证无法通过现有字段、hook 和机制表达。
+[T#B,!c47f17#边界]：换芯片、出现 OOM 或自定义 Runner 本身都不是充分证据。</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1041,19 +1051,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通全注意力：单层每token的有效KV字节数怎么算？</t>
+          <t xml:space="preserve">普通全注意力：单层每 token 有多少有效 KV 字节？</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：两份K/V乘KV head数Hkv、head维度D和每元素字节数s。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：两份 K/V 乘 KV head 数 Hkv、head 维度 D 和每元素字节数 s。
 [E##\mathrm{bytes/token/layer}=2H_{kv}Ds]
-[T#B,!c47f17#边界]：未计padding和额外元数据；K/V维度相同，不直接套用于MLA等不同存储结构。</t>
+[T#B,!c47f17#边界]：未计 padding 和额外元数据；K/V 维度相同，不直接套用于 MLA 等不同存储结构。</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用KV heads而非Query heads</t>
+          <t xml:space="preserve">使用 KV heads 而非 Query heads</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1065,13 +1075,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">末块未用槽位和页padding是同一种浪费吗？</t>
+          <t xml:space="preserve">末块空槽与物理 padding 怎样区分？</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是；前者来自请求未填满逻辑块，后者来自物理布局/跨度的额外占用。
-[T#B,!c47f17#边界]：应分项计账，避免重复加总。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：末块空槽属于逻辑块未填满；物理 padding 属于布局或页跨度的额外占用。
+• [T#B#例子]：35 tokens、B=16、3 KiB/token、64 KiB/单层页：有效数据 105 KiB，空槽 39 KiB，padding 48 KiB。
+[T#B,!c47f17#边界]：三项合计 192 KiB；分别计账，避免重复加总。</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1088,13 +1099,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">KV页跨度64 KiB，就表示每次设备分配至少64 KiB吗？</t>
+          <t xml:space="preserve">KV 页跨度为何不能代替设备分配粒度？</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：不能这样推断；页跨度、基址对齐和分配器取整是不同约束。
-[T#B,!c47f17#边界]：64 KiB是课堂题设，不是所有硬件或OS的默认要求。</t>
+[T#B,!c47f17#边界]：64 KiB 是课堂题设，不是所有硬件或 OS 的默认要求。</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1111,7 +1122,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">无共享时，多请求先合并token数再统一取整可以吗？</t>
+          <t xml:space="preserve">无共享的多请求 KV 块数，为什么要逐请求取整？</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1134,18 +1145,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5个pool block ID、32层，对应160个pool ID吗？</t>
+          <t xml:space="preserve">5 个 pool ID 在 32 层对应多少单层页？</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是；是5个pool ID对应160个单层物理页。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：对应 160 个单层物理页，pool ID 仍只有 5 个。
+[E##5\times32=160]
 [T#B,!c47f17#边界]：同规格单组、每层独立存储且无跨层共享的题设。</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID数与层页数</t>
+          <t xml:space="preserve">ID 数与层页数</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1157,12 +1169,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">R结束，但共享块仍被S引用，能覆盖这个块吗？</t>
+          <t xml:space="preserve">请求结束后，仍有活跃引用的共享 KV 块能被覆盖吗？</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；只解除R的引用，S的存活引用仍保护该块。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；只解除 R 的引用，S 的存活引用仍保护该块。
 [T#B,!c47f17#边界]：还需满足在途访问的安全回收条件。</t>
         </is>
       </c>
@@ -1180,13 +1192,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">有有效前缀KV的零引用块，能同时在free queue吗？</t>
+          <t xml:space="preserve">零引用的前缀缓存块为何还能留在 free queue？</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：可以；可再命中复用，也可在淘汰旧缓存标识后用于其他内容。
-[T#B,!c47f17#边界]：普通块，排除特殊保留块和未完成在途访问。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：零引用表示当前可再分配，不表示其中没有有效缓存数据。
+• [T#B#两条去向]：可被前缀命中后重新引用；也可先淘汰旧缓存标识，再供其他内容使用。
+[T#B,!c47f17#边界]：限定普通块，排除特殊保留块与尚有在途访问的情形。</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1196,20 +1209,21 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 K12；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 K12；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">查到前缀命中后，引用计数一定已增加吗？</t>
+          <t xml:space="preserve">查询前缀命中与正式建立引用有什么区别？</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不一定；后续容量检查失败时尚未正式引用，成功路径才touch。
-[T#B,!c47f17#边界]：正式复用需要建立引用；不能将“查询命中”与“已经占用”混用。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：查询只取得候选；通过容量检查后，正式复用才建立引用。
+• [T#B#成功路径]：先保护命中块，再分配新块。
+[T#B,!c47f17#边界]：容量检查失败时可能尚未增加引用，不能把“查询命中”与“已占用”混称。</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1219,20 +1233,21 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 K13；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 K13；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">pool空闲块为0，已有请求就一定不能再decode吗？</t>
+          <t xml:space="preserve">free queue 为空时，哪些 decode 步骤仍可能继续？</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不一定；末块仍有空槽位时，本步可以无需新增块。
-[T#B,!c47f17#边界]：仅从KV容量判断，其他调度条件仍须满足。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：末块仍有可用槽位、因而本步不需要新块的请求，仍可能继续。
+• [T#B#例子]：B=16：已有 47 个 KV tokens、占 3 块，再处理 1 token 无需新块；32 tokens、占 2 块则需新块。
+[T#B,!c47f17#边界]：这只判断 KV 容量，其他调度条件仍须满足。</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1249,13 +1264,13 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">第二块token相同，但之前前缀不同，能独立命中吗？</t>
+          <t xml:space="preserve">当前块 token 相同，为何仍需检查父前缀身份？</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能只凭当前块token判断；链式hash还包含父块身份及额外键。
-[T#B,!c47f17#边界]：上下文差异可影响整套模型KV；不声称每层K/V都必然依赖前文。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能只凭当前块 token 判断；链式 hash 还包含父块身份及额外键。
+[T#B,!c47f17#边界]：上下文差异可影响整套模型 KV；不声称每层 K/V 都必然依赖前文。</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1265,19 +1280,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 K09；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 K09；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">cache_salt不同，是否证明KV数值不同？</t>
+          <t xml:space="preserve">cache_salt 限定的是共享范围，还是 KV 数值？</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不证明；它限制允许共享的范围，即使数值可能相同也不跨域复用。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：限定允许共享的范围，不是判断 KV 数值是否相同。
+[T#B,!c47f17#边界]：salt 不同即不跨域复用，即使 KV 数值可能相同。</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1287,20 +1303,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 K09、K10；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 K09、K10；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">多租户服务为何可能隔离前缀缓存？</t>
+          <t xml:space="preserve">前缀缓存命中如何暴露跨租户信息？</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：命中带来的延迟差异可能暴露某段前缀是否已在缓存的统计线索。
-[T#B,!c47f17#边界]：隔离缓存共享不等于KV加密、身份认证或完整显存隔离。</t>
+[T#B,!c47f17#边界]：隔离缓存共享不等于 KV 加密、身份认证或完整显存隔离。</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1317,7 +1333,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">每个请求都换一个新salt，会损失什么？</t>
+          <t xml:space="preserve">每请求随机更换 salt 对前缀复用有什么影响？</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1340,12 +1356,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">关闭Prefix Cache，会失去分页KV访问能力吗？</t>
+          <t xml:space="preserve">Prefix Cache 与分页 KV 访问是什么关系？</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；分页访问与跨请求复用已计算前缀是不同功能。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：分页 KV 访问负责存储与寻址；Prefix Cache 负责复用已计算的前缀。
+[T#B,!c47f17#边界]：关闭前缀复用不会关闭分页访问；只启用分页也不会自动跳过重复 prefill。</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1362,13 +1379,13 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">前缀共享节省了活跃块，物理pool必须同步缩小吗？</t>
+          <t xml:space="preserve">前缀共享节省池内占用，为何不必缩小物理 pool？</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；省下的池内容量可以留给后续请求，预分配tensor仍保持。
-[T#B,!c47f17#边界]：pool按确定预算建立，不保证容纳所有未来请求。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；省下的池内容量可以留给后续请求，预分配 tensor 仍保持。
+[T#B,!c47f17#边界]：pool 按确定预算建立，不保证容纳所有未来请求。</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1385,17 +1402,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">512 B搬运单元能直接推出block size必须256 Token吗？</t>
+          <t xml:space="preserve">512 B 搬运粒度为何不能推出 256-token 分块？</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；字节粒度与token分块单位不同，还要结合dtype、head维度、布局和kernel设计。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；字节粒度与 token 分块单位不同，还要结合 dtype、head 维度、布局和 kernel 设计。</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytes与Token不直接等价</t>
+          <t xml:space="preserve">Bytes 与 Token 不直接等价</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1407,137 +1424,115 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">插件能否只把page_size_bytes替换成padded值？</t>
+          <t xml:space="preserve">DELTA 与 CUMULATIVE 的交付内容有何区别？</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能只换getter；原字段还用于逻辑tensor字节数反推块数，需一起调整消费者。
-[T#B,!c47f17#边界]：限定所查插件快照；统一物理页语义可讨论，但本轮未实现重构。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：DELTA 只包含新增生成内容；CUMULATIVE 包含截至当前的累计生成内容。
+[T#B,!c47f17#边界]：结果可能聚合，不保证每 token 一次交付或 SSE。</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">分子分母必须同口径</t>
+          <t xml:space="preserve">新增片段与累计快照</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 K05；vllm-cl 4fd99a4</t>
+          <t xml:space="preserve">全会话复盘 R03；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELTA和CUMULATIVE每份RequestOutput分别包含什么？</t>
+          <t xml:space="preserve">AsyncLLM.generate 的生成器消费什么结果？</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：DELTA只包含新增生成内容；CUMULATIVE包含截至当前的累计生成内容。
-[T#B,!c47f17#边界]：结果可能聚合，不保证每token一次交付或SSE。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它从 Collector 消费 RequestOutput，再向调用方 yield。
+[T#B,!c47f17#边界]：这是输出消费的异步生成器，不是模型 forward 或 Sampler。</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">新增片段与累计快照</t>
+          <t xml:space="preserve">消费输出的生成器</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 R03；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 R06；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">AsyncLLM.generate是在执行模型采样吗？</t>
+          <t xml:space="preserve">finished_req_ids 触发 Runner 清理哪类状态？</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是；这里的异步生成器从Collector消费RequestOutput，再向上yield。
-[T#B,!c47f17#边界]：不能因方法叫generate就把它当作模型forward或Sampler。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：移除结束请求的本地缓存状态与 InputBatch 成员，维护后续请求映射。
+[T#B,!c47f17#边界]：保留其他请求、模型权重、设备环境与物理 KV pool。</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费输出的生成器</t>
+          <t xml:space="preserve">请求级状态而非服务级资源</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 R06；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 R07；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ModelRunner收到finished_req_ids后清理什么？</t>
+          <t xml:space="preserve">最终 HTTP 输出是否需要等待 Runner 清理完成？</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：移除结束请求的本地缓存状态与InputBatch成员，维护后续请求映射。
-[T#B,!c47f17#边界]：保留其他请求、模型权重、设备环境与物理KV pool。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；两条后续路径没有这个互等要求。
+[T#B,!c47f17#边界]：不是允许永不清理；KV 回收仍须遵守在途访问的安全条件。</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">请求级状态而非服务级资源</t>
+          <t xml:space="preserve">无互等不等于无清理</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 R07；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 R08；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">最终HTTP输出必须等Runner完成本地状态清理吗？</t>
+          <t xml:space="preserve">零待算 token 的一步，Runner 如何清理结束请求？</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不必；两条后续路径没有这个互等要求。
-[T#B,!c47f17#边界]：不是允许永不清理；KV回收仍须遵守在途访问的安全条件。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先更新请求状态和处理结束通知，再判断是否跳过 forward。
+[T#B,!c47f17#边界]：所学 MRV1 路径允许在没有待计算 token 时完成请求级清理。</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">无互等不等于无清理</t>
+          <t xml:space="preserve">先更新状态，再跳过计算</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话复盘 R08；vllm v0.26.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">没有待计算token，Runner就不能清结束请求吗？</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：仍可清理；所学路径先更新状态，再判断是否跳过forward。</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">先更新状态，再跳过计算</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全会话复盘 R09；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话复盘 R09；vLLM v0.26.0</t>
         </is>
       </c>
     </row>
